--- a/交接班日志空模板.xlsx
+++ b/交接班日志空模板.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="127">
   <si>
     <t>数据中心交接班日志</t>
   </si>
@@ -118,9 +118,6 @@
   </si>
   <si>
     <t>闫昆</t>
-  </si>
-  <si>
-    <t>EA118机房E栋数据中心交接班日志</t>
   </si>
   <si>
     <t>日期</t>
@@ -2151,9 +2148,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:9">
-      <c r="A1" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -2165,13 +2160,13 @@
     </row>
     <row r="2" ht="12" customHeight="1" spans="1:9">
       <c r="A2" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -2180,18 +2175,18 @@
     </row>
     <row r="3" ht="12" customHeight="1" spans="1:9">
       <c r="A3" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>33</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
       <c r="E3" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G3" s="9"/>
       <c r="H3" s="10"/>
@@ -2209,7 +2204,7 @@
     </row>
     <row r="5" ht="12" customHeight="1" spans="1:9">
       <c r="A5" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -2222,53 +2217,53 @@
     </row>
     <row r="6" ht="12" customHeight="1" spans="1:9">
       <c r="A6" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="3"/>
     </row>
     <row r="7" ht="12" customHeight="1" spans="1:9">
       <c r="A7" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="3"/>
     </row>
     <row r="8" ht="12" customHeight="1" spans="1:9">
       <c r="A8" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="19"/>
@@ -2277,34 +2272,34 @@
     </row>
     <row r="9" ht="12" customHeight="1" spans="1:9">
       <c r="A9" s="21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9" s="22"/>
       <c r="C9" s="21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H9" s="25"/>
       <c r="I9" s="3"/>
     </row>
     <row r="10" ht="12" customHeight="1" spans="1:9">
       <c r="A10" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10" s="26"/>
       <c r="C10" s="27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D10" s="28"/>
       <c r="E10" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F10" s="29"/>
       <c r="G10" s="30"/>
@@ -2313,7 +2308,7 @@
     </row>
     <row r="11" ht="12" customHeight="1" spans="1:9">
       <c r="A11" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -2326,7 +2321,7 @@
     </row>
     <row r="12" ht="12" customHeight="1" spans="1:9">
       <c r="A12" s="32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" s="32"/>
       <c r="C12" s="32"/>
@@ -2338,33 +2333,33 @@
     </row>
     <row r="13" ht="12" customHeight="1" spans="1:9">
       <c r="A13" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B13" s="4">
         <v>1272</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" s="4">
         <v>2</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>60</v>
-      </c>
       <c r="H13" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" ht="12" customHeight="1" spans="1:9">
       <c r="A14" s="32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B14" s="32"/>
       <c r="C14" s="32"/>
@@ -2377,15 +2372,15 @@
     </row>
     <row r="15" ht="12" customHeight="1" spans="1:9">
       <c r="A15" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B15" s="33"/>
       <c r="C15" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F15" s="14"/>
       <c r="G15" s="14"/>
@@ -2394,7 +2389,7 @@
     </row>
     <row r="16" ht="12" customHeight="1" spans="1:9">
       <c r="A16" s="32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B16" s="32"/>
       <c r="C16" s="32"/>
@@ -2407,33 +2402,33 @@
     </row>
     <row r="17" ht="12" customHeight="1" spans="1:9">
       <c r="A17" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="C17" s="14" t="s">
         <v>67</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>68</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
       <c r="H17" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I17" s="3"/>
     </row>
     <row r="18" ht="12" customHeight="1" spans="1:9">
       <c r="A18" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B18" s="34" t="str">
         <f>IF(F2="白班","9:00","21:00")</f>
         <v>21:00</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
@@ -2447,14 +2442,14 @@
     </row>
     <row r="19" ht="12" customHeight="1" spans="1:9">
       <c r="A19" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B19" s="34" t="str">
         <f>IF(F2="白班","16:00","4:00")</f>
         <v>4:00</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
@@ -2468,7 +2463,7 @@
     </row>
     <row r="20" ht="12" customHeight="1" spans="1:9">
       <c r="A20" s="32" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B20" s="32"/>
       <c r="C20" s="32"/>
@@ -2481,24 +2476,24 @@
     </row>
     <row r="21" ht="12" customHeight="1" spans="1:9">
       <c r="A21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="C21" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="D21" s="14" t="s">
         <v>76</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>77</v>
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G21" s="33"/>
       <c r="H21" s="14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I21" s="3"/>
     </row>
@@ -2507,27 +2502,27 @@
         <v>1</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E22" s="14"/>
       <c r="F22" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G22" s="14"/>
       <c r="H22" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I22" s="3"/>
     </row>
     <row r="23" ht="12" customHeight="1" spans="1:9">
       <c r="A23" s="32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B23" s="32"/>
       <c r="C23" s="32"/>
@@ -2540,24 +2535,24 @@
     </row>
     <row r="24" ht="12" customHeight="1" spans="1:9">
       <c r="A24" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="14" t="s">
-        <v>75</v>
-      </c>
       <c r="C24" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E24" s="14"/>
       <c r="F24" s="33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G24" s="33"/>
       <c r="H24" s="14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" ht="12" customHeight="1" spans="1:9">
@@ -2565,27 +2560,27 @@
         <v>1</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" s="14"/>
       <c r="F25" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G25" s="14"/>
       <c r="H25" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I25" s="3"/>
     </row>
     <row r="26" ht="12" customHeight="1" spans="1:9">
       <c r="A26" s="32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
@@ -2598,22 +2593,22 @@
     </row>
     <row r="27" ht="12" customHeight="1" spans="1:9">
       <c r="A27" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E27" s="14"/>
       <c r="F27" s="14"/>
       <c r="G27" s="14"/>
       <c r="H27" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I27" s="3"/>
     </row>
@@ -2622,25 +2617,25 @@
         <v>1</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E28" s="14"/>
       <c r="F28" s="14"/>
       <c r="G28" s="14"/>
       <c r="H28" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I28" s="3"/>
     </row>
     <row r="29" ht="12" customHeight="1" spans="1:9">
       <c r="A29" s="32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B29" s="32"/>
       <c r="C29" s="32"/>
@@ -2653,22 +2648,22 @@
     </row>
     <row r="30" ht="12" customHeight="1" spans="1:9">
       <c r="A30" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B30" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="D30" s="14" t="s">
         <v>85</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>86</v>
       </c>
       <c r="E30" s="14"/>
       <c r="F30" s="14"/>
       <c r="G30" s="14"/>
       <c r="H30" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I30" s="3"/>
     </row>
@@ -2677,25 +2672,25 @@
         <v>1</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D31" s="39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E31" s="40"/>
       <c r="F31" s="40"/>
       <c r="G31" s="41"/>
       <c r="H31" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I31" s="3"/>
     </row>
     <row r="32" ht="12" customHeight="1" spans="1:9">
       <c r="A32" s="32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B32" s="32"/>
       <c r="C32" s="32"/>
@@ -2708,22 +2703,22 @@
     </row>
     <row r="33" ht="12" customHeight="1" spans="1:9">
       <c r="A33" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B33" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="D33" s="14" t="s">
         <v>89</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>90</v>
       </c>
       <c r="E33" s="14"/>
       <c r="F33" s="14"/>
       <c r="G33" s="14"/>
       <c r="H33" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I33" s="3"/>
     </row>
@@ -2732,25 +2727,25 @@
         <v>1</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D34" s="39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E34" s="40"/>
       <c r="F34" s="40"/>
       <c r="G34" s="41"/>
       <c r="H34" s="41" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I34" s="3"/>
     </row>
     <row r="35" ht="12" customHeight="1" spans="1:9">
       <c r="A35" s="32" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B35" s="32"/>
       <c r="C35" s="32"/>
@@ -2763,26 +2758,26 @@
     </row>
     <row r="36" ht="12" customHeight="1" spans="1:9">
       <c r="A36" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B36" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D36" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="C36" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D36" s="14" t="s">
+      <c r="E36" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="F36" s="14" t="s">
         <v>94</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>95</v>
       </c>
       <c r="G36" s="14"/>
       <c r="H36" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I36" s="3"/>
     </row>
@@ -2791,29 +2786,29 @@
         <v>1</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G37" s="14"/>
       <c r="H37" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I37" s="3"/>
     </row>
     <row r="38" ht="12" customHeight="1" spans="1:9">
       <c r="A38" s="32" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B38" s="32"/>
       <c r="C38" s="32"/>
@@ -2826,23 +2821,23 @@
     </row>
     <row r="39" ht="12" customHeight="1" spans="1:9">
       <c r="A39" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C39" s="14"/>
       <c r="D39" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E39" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="F39" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="F39" s="14" t="s">
+      <c r="G39" s="14" t="s">
         <v>101</v>
-      </c>
-      <c r="G39" s="14" t="s">
-        <v>102</v>
       </c>
       <c r="H39" s="14"/>
       <c r="I39" s="3"/>
@@ -2852,27 +2847,27 @@
         <v>1</v>
       </c>
       <c r="B40" s="39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C40" s="41"/>
       <c r="D40" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G40" s="39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H40" s="41"/>
       <c r="I40" s="3"/>
     </row>
     <row r="41" ht="12" customHeight="1" spans="1:9">
       <c r="A41" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B41" s="32"/>
       <c r="C41" s="32"/>
@@ -2885,20 +2880,20 @@
     </row>
     <row r="42" ht="12" customHeight="1" spans="1:9">
       <c r="A42" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C42" s="14"/>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G42" s="14"/>
       <c r="H42" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I42" s="3"/>
     </row>
@@ -2907,23 +2902,23 @@
         <v>1</v>
       </c>
       <c r="B43" s="42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C43" s="42"/>
       <c r="D43" s="42"/>
       <c r="E43" s="42"/>
       <c r="F43" s="42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G43" s="42"/>
       <c r="H43" s="42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I43" s="3"/>
     </row>
     <row r="44" ht="12" customHeight="1" spans="1:9">
       <c r="A44" s="32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B44" s="32"/>
       <c r="C44" s="32"/>
@@ -2936,20 +2931,20 @@
     </row>
     <row r="45" ht="12" customHeight="1" spans="1:9">
       <c r="A45" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C45" s="14"/>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G45" s="14"/>
       <c r="H45" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I45" s="3"/>
     </row>
@@ -2958,23 +2953,23 @@
         <v>1</v>
       </c>
       <c r="B46" s="42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C46" s="42"/>
       <c r="D46" s="42"/>
       <c r="E46" s="42"/>
       <c r="F46" s="42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G46" s="42"/>
       <c r="H46" s="42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I46" s="3"/>
     </row>
     <row r="47" ht="12" customHeight="1" spans="1:9">
       <c r="A47" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B47" s="13"/>
       <c r="C47" s="13"/>
@@ -2987,10 +2982,10 @@
     </row>
     <row r="48" ht="12" customHeight="1" spans="1:9">
       <c r="A48" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C48" s="14"/>
       <c r="D48" s="14"/>
@@ -2998,7 +2993,7 @@
       <c r="F48" s="14"/>
       <c r="G48" s="14"/>
       <c r="H48" s="14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I48" s="3"/>
     </row>
@@ -3007,7 +3002,7 @@
         <v>1</v>
       </c>
       <c r="B49" s="43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49" s="43"/>
       <c r="D49" s="43"/>
@@ -3015,13 +3010,13 @@
       <c r="F49" s="43"/>
       <c r="G49" s="43"/>
       <c r="H49" s="33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I49" s="3"/>
     </row>
     <row r="50" ht="15.95" customHeight="1" spans="1:9">
       <c r="A50" s="44" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B50" s="44"/>
       <c r="C50" s="44"/>
@@ -3034,46 +3029,46 @@
     </row>
     <row r="51" ht="12" customHeight="1" spans="1:9">
       <c r="A51" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B51" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="C51" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F51" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="F51" s="45" t="s">
+      <c r="G51" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="H51" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>115</v>
       </c>
       <c r="I51" s="3"/>
     </row>
     <row r="52" ht="12" customHeight="1" spans="1:9">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>117</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4">
         <v>1</v>
       </c>
       <c r="F52" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="G52" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="H52" s="46"/>
       <c r="I52" s="3"/>
@@ -3081,20 +3076,20 @@
     <row r="53" ht="12" customHeight="1" spans="1:9">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4">
         <v>5</v>
       </c>
       <c r="F53" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="G53" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="H53" s="46"/>
       <c r="I53" s="3"/>
@@ -3102,20 +3097,20 @@
     <row r="54" ht="12" customHeight="1" spans="1:9">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C54" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>122</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4">
         <v>4</v>
       </c>
       <c r="F54" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G54" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="H54" s="46"/>
       <c r="I54" s="3"/>
@@ -3123,36 +3118,36 @@
     <row r="55" ht="12" customHeight="1" spans="1:9">
       <c r="A55" s="4"/>
       <c r="B55" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="4">
         <v>1</v>
       </c>
       <c r="F55" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G55" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="H55" s="46"/>
       <c r="I55" s="3"/>
     </row>
     <row r="56" ht="12" customHeight="1" spans="1:9">
       <c r="A56" s="47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B56" s="47"/>
       <c r="C56" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D56" s="48"/>
       <c r="E56" s="49"/>
       <c r="F56" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G56" s="48"/>
       <c r="H56" s="49"/>
@@ -3165,7 +3160,7 @@
       <c r="D57" s="50"/>
       <c r="E57" s="50"/>
       <c r="F57" s="51" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G57" s="52"/>
       <c r="H57" s="50"/>
@@ -3267,7 +3262,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1d51a5b6-13bb-44f6-b7f9-3b5993e10b67}</x14:id>
+          <x14:id>{632b9989-5af6-46f0-b6ac-3c61f14067ce}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3289,7 +3284,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1d51a5b6-13bb-44f6-b7f9-3b5993e10b67}">
+          <x14:cfRule type="dataBar" id="{632b9989-5af6-46f0-b6ac-3c61f14067ce}">
             <x14:dataBar minLength="0" maxLength="100" border="1" direction="leftToRight">
               <x14:cfvo type="num">
                 <xm:f>1</xm:f>
